--- a/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 5,3</t>
+          <t>-2,27; 5,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 7,61</t>
+          <t>-1,32; 7,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 6,04</t>
+          <t>-0,93; 6,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,97</t>
+          <t>-4,54; 2,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,84</t>
+          <t>-3,45; 5,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 3,83</t>
+          <t>-3,73; 3,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,95</t>
+          <t>-2,46; 2,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,78</t>
+          <t>-1,11; 5,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,94</t>
+          <t>-1,43; 4,13</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 840,28</t>
+          <t>-59,34; 846,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 702,82</t>
+          <t>-46,33; 674,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-86,62; 322,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,11; 542,73</t>
+          <t>-78,44; 386,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,86; 344,65</t>
+          <t>-73,4; 360,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 206,55</t>
+          <t>-66,92; 172,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 303,95</t>
+          <t>-34,11; 286,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,68; 263,75</t>
+          <t>-36,95; 271,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,48</t>
+          <t>-4,13; 1,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 4,72</t>
+          <t>-1,27; 5,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,82</t>
+          <t>-1,3; 5,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-4,05; -0,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,48</t>
+          <t>0,14; 6,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,86</t>
+          <t>0,61; 6,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,16</t>
+          <t>-2,93; 0,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,71</t>
+          <t>0,15; 4,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,27</t>
+          <t>0,81; 5,23</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 207,51</t>
+          <t>-100,0; 246,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,35; 401,0</t>
+          <t>-39,87; 573,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 541,69</t>
+          <t>-45,58; 499,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 1063,56</t>
+          <t>-25,04; 984,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1120,1</t>
+          <t>-1,35; 1063,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,85; 42,03</t>
+          <t>-90,8; 51,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 370,71</t>
+          <t>0,6; 405,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,45; 423,87</t>
+          <t>18,69; 424,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,96</t>
+          <t>-2,64; 4,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 9,03</t>
+          <t>-0,1; 8,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 6,94</t>
+          <t>-0,86; 6,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,3</t>
+          <t>-6,64; 0,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,58</t>
+          <t>-4,27; 3,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,81</t>
+          <t>-1,85; 6,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,04</t>
+          <t>-3,44; 1,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,9</t>
+          <t>-0,85; 5,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 5,57</t>
+          <t>-0,46; 5,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,62; 604,67</t>
+          <t>-78,9; 594,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 1148,48</t>
+          <t>-24,16; 984,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,88; 868,35</t>
+          <t>-31,75; 845,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 48,08</t>
+          <t>-100,0; 32,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 152,44</t>
+          <t>-68,51; 188,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 293,61</t>
+          <t>-34,86; 280,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 65,71</t>
+          <t>-76,16; 72,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 242,08</t>
+          <t>-20,14; 274,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 261,14</t>
+          <t>-12,96; 269,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,32</t>
+          <t>-0,69; 5,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 6,07</t>
+          <t>-0,21; 6,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,8</t>
+          <t>1,9; 9,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,49</t>
+          <t>-3,37; 1,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 7,81</t>
+          <t>0,4; 7,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,42</t>
+          <t>0,98; 9,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,9</t>
+          <t>-1,31; 2,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,14</t>
+          <t>0,78; 5,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,62</t>
+          <t>2,61; 8,2</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 996,42</t>
+          <t>-41,88; 878,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,03; 905,97</t>
+          <t>-27,12; 978,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,95; 1720,77</t>
+          <t>42,34; 1694,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 268,69</t>
+          <t>-100,0; 230,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1035,63</t>
+          <t>-10,64; 862,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,62; 1132,04</t>
+          <t>8,45; 1009,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,62; 277,98</t>
+          <t>-51,54; 234,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,38; 541,64</t>
+          <t>17,68; 534,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84,99; 791,36</t>
+          <t>58,92; 738,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,54</t>
+          <t>-0,82; 2,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,86</t>
+          <t>0,99; 4,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,98</t>
+          <t>1,49; 5,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; -0,02</t>
+          <t>-2,64; -0,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,88</t>
+          <t>0,24; 3,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,06</t>
+          <t>1,29; 4,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,74</t>
+          <t>-1,36; 0,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,81</t>
+          <t>1,08; 3,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,43</t>
+          <t>1,86; 4,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 162,54</t>
+          <t>-30,3; 154,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31,39; 321,6</t>
+          <t>22,01; 305,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39,92; 339,12</t>
+          <t>44,25; 343,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 3,74</t>
+          <t>-76,48; 7,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,51; 207,97</t>
+          <t>5,83; 202,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,01; 269,31</t>
+          <t>35,55; 239,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 38,9</t>
+          <t>-46,46; 37,6</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>38,33; 195,61</t>
+          <t>35,97; 184,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>60,49; 224,23</t>
+          <t>58,08; 229,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 5,02</t>
+          <t>-2,43; 5,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 7,26</t>
+          <t>-0,86; 7,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 6,35</t>
+          <t>-1,54; 5,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 2,54</t>
+          <t>-4,53; 3,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 5,24</t>
+          <t>-3,3; 5,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,79</t>
+          <t>-3,42; 4,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,78</t>
+          <t>-2,35; 2,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,06</t>
+          <t>-1,37; 4,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,13</t>
+          <t>-1,58; 4,14</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,34; 846,71</t>
+          <t>-43,8; 918,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 674,22</t>
+          <t>-47,7; 625,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,28; 264,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,44; 386,07</t>
+          <t>-80,01; 445,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,4; 360,56</t>
+          <t>-72,47; 338,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,92; 172,19</t>
+          <t>-60,68; 200,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 286,69</t>
+          <t>-36,09; 313,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,95; 271,59</t>
+          <t>-39,08; 249,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,93</t>
+          <t>-4,1; 1,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,35</t>
+          <t>-1,81; 5,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 5,2</t>
+          <t>-1,21; 5,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; -0,02</t>
+          <t>-4,14; 0,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,24</t>
+          <t>0,1; 6,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,88</t>
+          <t>0,52; 6,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,38</t>
+          <t>-3,23; 0,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,74</t>
+          <t>0,08; 4,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,23</t>
+          <t>0,48; 5,18</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 246,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 573,11</t>
+          <t>-55,04; 553,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,58; 499,0</t>
+          <t>-40,19; 544,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 984,03</t>
+          <t>-18,88; 1015,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1063,34</t>
+          <t>3,61; 1090,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-90,8; 51,57</t>
+          <t>-91,22; 43,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 405,2</t>
+          <t>-5,52; 390,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,69; 424,51</t>
+          <t>0,71; 388,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 4,0</t>
+          <t>-2,78; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 8,38</t>
+          <t>0,39; 8,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 6,56</t>
+          <t>-0,7; 6,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 0,38</t>
+          <t>-6,21; 0,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 3,91</t>
+          <t>-3,82; 3,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 6,53</t>
+          <t>-1,75; 6,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,33</t>
+          <t>-3,59; 1,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,21</t>
+          <t>-1,1; 4,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 5,65</t>
+          <t>-0,45; 5,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,9; 594,58</t>
+          <t>-81,35; 495,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 984,09</t>
+          <t>-21,01; 936,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 845,87</t>
+          <t>-30,26; 779,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,98</t>
+          <t>-91,41; 64,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 188,0</t>
+          <t>-66,33; 176,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 280,51</t>
+          <t>-30,05; 342,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,16; 72,07</t>
+          <t>-78,07; 68,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 274,29</t>
+          <t>-27,79; 255,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 269,42</t>
+          <t>-12,74; 294,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,67</t>
+          <t>-0,58; 6,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 6,13</t>
+          <t>-0,19; 6,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 9,8</t>
+          <t>1,93; 9,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,53</t>
+          <t>-3,41; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 7,63</t>
+          <t>0,17; 7,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,53</t>
+          <t>0,95; 8,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,71</t>
+          <t>-1,12; 2,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,74</t>
+          <t>0,77; 5,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,2</t>
+          <t>2,63; 8,26</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 878,35</t>
+          <t>-49,04; 1069,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 978,69</t>
+          <t>-30,61; 1095,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42,34; 1694,25</t>
+          <t>31,48; 1656,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,82</t>
+          <t>-100,0; 230,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 862,46</t>
+          <t>-18,39; 722,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,45; 1009,0</t>
+          <t>12,42; 888,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-51,54; 234,19</t>
+          <t>-43,82; 284,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,68; 534,08</t>
+          <t>13,37; 547,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58,92; 738,69</t>
+          <t>77,27; 760,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,5</t>
+          <t>-0,65; 2,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,77</t>
+          <t>1,1; 4,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,04</t>
+          <t>1,33; 4,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,01</t>
+          <t>-2,78; 0,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,91</t>
+          <t>0,31; 3,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,83</t>
+          <t>1,23; 4,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,73</t>
+          <t>-1,39; 0,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,65</t>
+          <t>1,11; 3,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,41</t>
+          <t>1,82; 4,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 154,55</t>
+          <t>-26,67; 173,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22,01; 305,45</t>
+          <t>35,41; 337,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44,25; 343,91</t>
+          <t>35,65; 337,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 7,11</t>
+          <t>-76,8; 11,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,83; 202,8</t>
+          <t>1,29; 197,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,55; 239,55</t>
+          <t>33,31; 259,85</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,46; 37,6</t>
+          <t>-46,86; 36,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>35,97; 184,39</t>
+          <t>37,86; 204,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>58,08; 229,53</t>
+          <t>56,49; 225,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,49</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,81</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,45</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 5,27</t>
+          <t>-4,55; 2,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 7,99</t>
+          <t>-3,28; 4,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,92</t>
+          <t>-3,72; 4,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 3,13</t>
+          <t>-2,66; 5,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 5,32</t>
+          <t>-0,89; 7,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 4,0</t>
+          <t>-1,05; 6,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,97</t>
+          <t>-2,61; 2,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,92</t>
+          <t>-1,18; 4,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,14</t>
+          <t>-1,23; 4,55</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-19,45%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,39%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>43,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>121,05%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>103,71%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-19,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>107,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>52,54%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-86,62; 322,66</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-78,11; 542,73</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-72,28; 444,64</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-43,8; 918,03</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-47,7; 625,2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-86,28; 264,18</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,01; 445,17</t>
+          <t>-45,78; 840,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,47; 338,85</t>
+          <t>-46,23; 716,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 200,48</t>
+          <t>-64,44; 206,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 313,42</t>
+          <t>-32,13; 303,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 249,98</t>
+          <t>-37,63; 278,78</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,06</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,06</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,78</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>3,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,91</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 5,0</t>
+          <t>0,15; 6,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 5,14</t>
+          <t>1,24; 7,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,36</t>
+          <t>-4,08; 1,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,38</t>
+          <t>-1,97; 4,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,87</t>
+          <t>-1,11; 5,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,17</t>
+          <t>-3,01; 0,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,82</t>
+          <t>0,19; 4,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,18</t>
+          <t>1,12; 5,85</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-77,32%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>165,84%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>227,87%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-41,45%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>69,96%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>71,4%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-77,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>165,84%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>201,92%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>132,43%</t>
+          <t>151,85%</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,04; 553,04</t>
+          <t>-19,65; 1063,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 544,9</t>
+          <t>6,57; 1198,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 207,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 1015,54</t>
+          <t>-54,35; 401,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 1090,71</t>
+          <t>-40,76; 540,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-91,22; 43,79</t>
+          <t>-89,85; 42,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 390,77</t>
+          <t>-4,19; 370,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 388,95</t>
+          <t>22,8; 474,84</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,71</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,42</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>4,25</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,88</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,45</t>
+          <t>4,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>3,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,77</t>
+          <t>-6,4; 0,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 8,32</t>
+          <t>-4,02; 3,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,68</t>
+          <t>-1,68; 6,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 0,33</t>
+          <t>-2,71; 3,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,88</t>
+          <t>0,54; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,78</t>
+          <t>0,08; 8,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,15</t>
+          <t>-3,73; 1,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,95</t>
+          <t>-0,89; 4,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,68</t>
+          <t>0,24; 6,15</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-64,4%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-3,02%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>57,49%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>27,39%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>185,91%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>125,98%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-64,4%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-3,02%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>176,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-81,35; 495,36</t>
+          <t>-100,0; 48,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 936,72</t>
+          <t>-66,99; 152,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 779,36</t>
+          <t>-31,58; 307,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-91,41; 64,26</t>
+          <t>-78,62; 604,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,33; 176,83</t>
+          <t>-10,09; 1148,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 342,43</t>
+          <t>-15,26; 1046,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,07; 68,54</t>
+          <t>-77,83; 65,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 255,66</t>
+          <t>-24,39; 242,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 294,17</t>
+          <t>-0,55; 292,83</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,59</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,07</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,34</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,72</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 6,12</t>
+          <t>-3,38; 1,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 6,12</t>
+          <t>0,3; 7,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,71</t>
+          <t>1,24; 10,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,51</t>
+          <t>-0,49; 6,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 7,49</t>
+          <t>-0,17; 6,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,95</t>
+          <t>2,1; 10,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,82</t>
+          <t>-1,21; 2,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,68</t>
+          <t>0,86; 6,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,26</t>
+          <t>2,93; 9,05</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-35,82%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>167,26%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>236,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>132,8%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>154,55%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>318,32%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-35,82%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>167,26%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>221,5%</t>
+          <t>335,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>265,61%</t>
+          <t>281,68%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 1069,65</t>
+          <t>-100,0; 268,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 1095,6</t>
+          <t>-2,61; 1035,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,48; 1656,58</t>
+          <t>15,92; 1200,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,3</t>
+          <t>-39,96; 996,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 722,13</t>
+          <t>-37,03; 905,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,42; 888,16</t>
+          <t>41,66; 1804,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 284,94</t>
+          <t>-50,62; 277,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,37; 547,22</t>
+          <t>19,38; 541,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77,27; 760,04</t>
+          <t>95,55; 847,63</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,01</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,31</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,82</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,52</t>
+          <t>-2,86; -0,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,81</t>
+          <t>0,29; 3,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,99</t>
+          <t>1,39; 5,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,11</t>
+          <t>-0,74; 2,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,96</t>
+          <t>1,05; 4,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,99</t>
+          <t>1,77; 5,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,73</t>
+          <t>-1,34; 0,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,78</t>
+          <t>1,19; 3,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,57</t>
+          <t>2,2; 4,93</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-49,76%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>120,94%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>36,1%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>128,97%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>147,72%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-49,76%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>73,52%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>110,54%</t>
+          <t>171,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>126,91%</t>
+          <t>142,73%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 173,05</t>
+          <t>-79,12; 3,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>35,41; 337,16</t>
+          <t>4,51; 207,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35,65; 337,08</t>
+          <t>33,89; 288,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 11,51</t>
+          <t>-26,92; 162,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,29; 197,57</t>
+          <t>31,39; 321,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,31; 259,85</t>
+          <t>51,6; 361,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 36,23</t>
+          <t>-44,46; 38,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>37,86; 204,28</t>
+          <t>38,33; 195,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>56,49; 225,4</t>
+          <t>72,17; 249,98</t>
         </is>
       </c>
     </row>
